--- a/artfynd/A 26001-2026 artfynd.xlsx
+++ b/artfynd/A 26001-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61209274</v>
+        <v>61209617</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vattholma gård, 1,8 km NO-ut, Upl</t>
+          <t>Vattholma gård, 2,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656136.1790419191</v>
+        <v>656526</v>
       </c>
       <c r="R2" t="n">
-        <v>6657657.138097807</v>
+        <v>6657517</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,21 +752,11 @@
           <t>2016-08-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-08-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -776,22 +768,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>skogslind</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Tilia cordata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Tilia cordata</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -813,15 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61209275</v>
+        <v>61209618</v>
       </c>
       <c r="B3" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,36 +816,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vattholma gård, 1,8 km NO-ut, Upl</t>
+          <t>Vattholma gård, 2,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656136.1790419191</v>
+        <v>656526</v>
       </c>
       <c r="R3" t="n">
-        <v>6657657.138097807</v>
+        <v>6657517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,21 +882,11 @@
           <t>2016-08-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-08-28</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -914,22 +898,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>skogslind</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Tilia cordata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Tilia cordata</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,12 +938,7 @@
         <v>61209137</v>
       </c>
       <c r="B4" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656190.2515157794</v>
+        <v>656190</v>
       </c>
       <c r="R4" t="n">
-        <v>6657516.808997172</v>
+        <v>6657517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,19 +1006,9 @@
           <t>2016-08-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-08-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,15 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61209276</v>
+        <v>61985691</v>
       </c>
       <c r="B5" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,40 +1050,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vattholma gård, 1,8 km NO-ut, Upl</t>
+          <t>Vattholma gård, 1,9 km NO-ut, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656136.1790419191</v>
+        <v>656175</v>
       </c>
       <c r="R5" t="n">
-        <v>6657657.138097807</v>
+        <v>6657805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,22 +1104,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-08-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-08-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,26 +1120,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>skogslind</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Tilia cordata</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Tilia cordata</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1201,7 +1129,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Sofia Lundell, Mattias Lif, Thorleif Joelson, Jörgen Sjöström</t>
+          <t>Henry Åkerström, Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1212,15 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61209159</v>
+        <v>125542441</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90681</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,37 +1151,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6268</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vattholma gård, 1,8 km NO-ut, Upl</t>
+          <t>Lafsen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656136.1790419191</v>
+        <v>656302</v>
       </c>
       <c r="R6" t="n">
-        <v>6657657.138097807</v>
+        <v>6657593</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,22 +1216,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-08-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-08-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1309,78 +1230,70 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Sofia Lundell, Mattias Lif, Thorleif Joelson, Jörgen Sjöström</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+          <t>Fynd med DNA-sekvens - 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125542441</v>
+        <v>61209274</v>
       </c>
       <c r="B7" t="n">
-        <v>89979</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6268</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lafsen, Upl</t>
+          <t>Vattholma gård, 1,8 km NO-ut, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656302</v>
+        <v>656136</v>
       </c>
       <c r="R7" t="n">
-        <v>6657593</v>
+        <v>6657657</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,12 +1320,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2016-08-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2016-08-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,24 +1334,397 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogslind</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Tilia cordata</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Tilia cordata</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Henry Åkerström, Sofia Lundell, Mattias Lif, Thorleif Joelson, Jörgen Sjöström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Fynd med DNA-sekvens - 1</t>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>61209275</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vattholma gård, 1,8 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>656136</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6657657</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rasbokil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-08-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-08-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>skogslind</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Tilia cordata</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Tilia cordata</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Sofia Lundell, Mattias Lif, Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>61209159</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vattholma gård, 1,8 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>656136</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6657657</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rasbokil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-08-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-08-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Sofia Lundell, Mattias Lif, Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>61209276</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vattholma gård, 1,8 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>656136</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6657657</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rasbokil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-08-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-08-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>skogslind</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Tilia cordata</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Tilia cordata</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Sofia Lundell, Mattias Lif, Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
     </row>
